--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N81_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N81_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.00572407932879</v>
+        <v>5.200930162890929</v>
       </c>
       <c r="D2" t="n">
-        <v>32.97017807927963</v>
+        <v>5.357653937882939</v>
       </c>
       <c r="E2" t="n">
-        <v>5.463351549009573</v>
+        <v>0.8877946267140556</v>
       </c>
       <c r="F2" t="n">
-        <v>5.260889732204956</v>
+        <v>0.8548945814833052</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.76885107504321</v>
+        <v>3.537438299694521</v>
       </c>
       <c r="D3" t="n">
-        <v>22.90623423056361</v>
+        <v>3.722263062466587</v>
       </c>
       <c r="E3" t="n">
-        <v>5.463351549009573</v>
+        <v>0.8877946267140556</v>
       </c>
       <c r="F3" t="n">
-        <v>5.260889732204956</v>
+        <v>0.8548945814833052</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.55146430479975</v>
+        <v>4.31461294952996</v>
       </c>
       <c r="D4" t="n">
-        <v>27.17505866696014</v>
+        <v>4.415947033381022</v>
       </c>
       <c r="E4" t="n">
-        <v>5.463351549009573</v>
+        <v>0.8877946267140556</v>
       </c>
       <c r="F4" t="n">
-        <v>5.260889732204956</v>
+        <v>0.8548945814833052</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.64545898468008</v>
+        <v>3.192387085010513</v>
       </c>
       <c r="D5" t="n">
-        <v>20.39087870816177</v>
+        <v>3.313517790076288</v>
       </c>
       <c r="E5" t="n">
-        <v>5.463351549009573</v>
+        <v>0.8877946267140556</v>
       </c>
       <c r="F5" t="n">
-        <v>5.260889732204956</v>
+        <v>0.8548945814833052</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.12919685917002</v>
+        <v>2.458494489615129</v>
       </c>
       <c r="D6" t="n">
-        <v>17.52290690642855</v>
+        <v>2.847472372294639</v>
       </c>
       <c r="E6" t="n">
-        <v>5.463351549009573</v>
+        <v>0.8877946267140556</v>
       </c>
       <c r="F6" t="n">
-        <v>5.260889732204956</v>
+        <v>0.8548945814833052</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.44403357300792</v>
+        <v>3.159655455613788</v>
       </c>
       <c r="D7" t="n">
-        <v>19.3521999810505</v>
+        <v>3.144732496920706</v>
       </c>
       <c r="E7" t="n">
-        <v>5.463351549009573</v>
+        <v>0.8877946267140556</v>
       </c>
       <c r="F7" t="n">
-        <v>5.260889732204956</v>
+        <v>0.8548945814833052</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
